--- a/stories/arbres/ATOM-SEC.MAI.002-03.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Marin est au jardin avec maman. Il voit une baie brillante. Il ne la connaît pas. C'est inconnu. Marin ne goûte pas tout seul. Il va demander. Il dit : maman, je peux ? Maman, c'est l'adulte. Maman regarde. Elle dit : on laisse. Merci d'avoir demandé. Marin pose ses mains avec les feuilles. Inconnu : on demande à l'adulte.</t>
+          <t>Marin est au jardin avec maman. Il voit une baie brillante. Il ne la connaît pas. C'est inconnu. Marin ne goûte pas tout seul. Il va demander. Maman, je peux ? Maman, c'est l'adulte. Maman regarde. On laisse. Merci d'avoir demandé. Marin pose ses mains avec les feuilles. Inconnu : on demande à l'adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Marin est au jardin avec maman. Il voit une baie brillante. Il ne la connaît pas. C'est inconnu. Marin ne goûte pas tout seul. Il va demander.
+narrateur|Maman, je peux ? Maman, c'est l'adulte. Maman regarde.
+narrateur|On laisse. Merci d'avoir demandé.
+narrateur|Marin pose ses mains avec les feuilles. Inconnu : on demande à l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1473,6 +1497,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Marin voit une baie inconnue. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1645,6 +1674,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Marin a demandé. L'inconnu, on le dit à l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1841,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman donne une fraise du panier. Marin dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2008,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2048,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.002-03.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 narrateur|Marin pose ses mains avec les feuilles. Inconnu : on demande à l'adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1504,6 +1510,7 @@
           <t>narrateur|Marin voit une baie inconnue. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1679,6 +1686,7 @@
           <t>narrateur|Marin a demandé. L'inconnu, on le dit à l'adulte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1846,6 +1854,7 @@
           <t>narrateur|Maman donne une fraise du panier. Marin dit merci.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2013,6 +2022,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2031,7 +2041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2055,6 +2065,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2256,6 +2280,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.MAI.002-03.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Marin demande avant de goûter</t>
+          <t>La baie de Nina</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>L'arrosoir penche dans l'herbe. Nina voit une baie brillante. Elle demande à maman. On laisse. Maman donne une fraise du panier.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Marin est au jardin avec maman. Il voit une baie brillante. Il ne la connaît pas. C'est inconnu. Marin ne goûte pas tout seul. Il va demander. Maman, je peux ? Maman, c'est l'adulte. Maman regarde. On laisse. Merci d'avoir demandé. Marin pose ses mains avec les feuilles. Inconnu : on demande à l'adulte.</t>
+          <t>L'arrosoir penche dans l'herbe mouillée. Une goutte tombe sur une feuille. Une abeille passe tout près, tout doux. Le panier sent la terre tiède. Au loin, le marché fait un petit bruit. Nina, tu as vu l'herbe ? Oui, maman. Elle brille. Elle brille, après la pluie. Le jardin sent la terre mouillée. Un seau bleu est près du banc. Tu as vu le seau bleu ? Oui. Il est plein. Il est plein d'eau douce. En ce moment, Nina est au jardin. Ses chaussures sont un peu humides. Elle voit une baie brillante. La baie est ronde et rouge. Nina ne la connaît pas. C'est de l'inconnu. Nina pose les mains sur ses genoux. Elle va demander. Maman, je peux ? Tu demandes. C'est bien. Maman, c'est l'adulte. Maman regarde la baie. On laisse. Merci d'avoir demandé. On demande à l'adulte. Nina pose ses mains avec les feuilles. Les feuilles sont fraîches et lisses. On laisse, maman. Oui. Inconnu : on demande à l'adulte. Bravo, Nina. Maman ouvre le panier. Une fraise rouge attend. Celle-ci, tu la connais. Tu peux goûter. Nina prend la fraise. Elle est douce et un peu froide. Nina croque. C'est sucré. Merci, maman. Tu as fait du bon travail. Tu as demandé. L'arrosoir penche encore. L'abeille est déjà loin. Le seau bleu reste près du banc.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,13 +1324,55 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Marin est au jardin avec maman. Il voit une baie brillante. Il ne la connaît pas. C'est inconnu. Marin ne goûte pas tout seul. Il va demander.
-narrateur|Maman, je peux ? Maman, c'est l'adulte. Maman regarde.
-narrateur|On laisse. Merci d'avoir demandé.
-narrateur|Marin pose ses mains avec les feuilles. Inconnu : on demande à l'adulte.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|L'arrosoir penche dans l'herbe mouillée.
+narrateur|Une goutte tombe sur une feuille.
+narrateur|Une abeille passe tout près, tout doux.
+narrateur|Le panier sent la terre tiède.
+narrateur|Au loin, le marché fait un petit bruit.
+maman|Nina, tu as vu l'herbe ?
+enfant-f|Oui, maman. Elle brille.
+maman|Elle brille, après la pluie.
+narrateur|Le jardin sent la terre mouillée.
+narrateur|Un seau bleu est près du banc.
+maman|Tu as vu le seau bleu ?
+enfant-f|Oui. Il est plein.
+maman|Il est plein d'eau douce.
+narrateur|En ce moment, Nina est au jardin.
+narrateur|Ses chaussures sont un peu humides.
+narrateur|Elle voit une baie brillante.
+narrateur|La baie est ronde et rouge.
+narrateur|Nina ne la connaît pas.
+narrateur|C'est de l'inconnu.
+narrateur|Nina pose les mains sur ses genoux.
+narrateur|Elle va demander.
+enfant-f|Maman, je peux ?
+maman|Tu demandes. C'est bien.
+narrateur|Maman, c'est l'adulte.
+narrateur|Maman regarde la baie.
+maman|On laisse.
+maman|Merci d'avoir demandé.
+maman|On demande à l'adulte.
+narrateur|Nina pose ses mains avec les feuilles.
+narrateur|Les feuilles sont fraîches et lisses.
+enfant-f|On laisse, maman.
+maman|Oui. Inconnu : on demande à l'adulte.
+maman|Bravo, Nina.
+narrateur|Maman ouvre le panier.
+narrateur|Une fraise rouge attend.
+maman|Celle-ci, tu la connais.
+maman|Tu peux goûter.
+narrateur|Nina prend la fraise.
+narrateur|Elle est douce et un peu froide.
+narrateur|Nina croque.
+narrateur|C'est sucré.
+enfant-f|Merci, maman.
+maman|Tu as fait du bon travail.
+maman|Tu as demandé.
+narrateur|L'arrosoir penche encore.
+narrateur|L'abeille est déjà loin.
+narrateur|Le seau bleu reste près du banc.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1343,7 +1397,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Marin voit une baie inconnue. Que fait-il ?</t>
+          <t>Nina voit une baie inconnue. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1507,10 +1561,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Marin voit une baie inconnue. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Nina voit une baie inconnue.
+narrateur|Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1535,7 +1589,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Marin a demandé. L'inconnu, on le dit à l'adulte.</t>
+          <t>Nina a demandé. L'inconnu, on le dit à l'adulte. Tu as demandé à maman ? Oui. Bravo. On demande à l'adulte. La fraise était dans le panier. L'herbe brille encore. Le seau bleu est calme. Tes mains étaient avec les feuilles ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1683,10 +1737,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Marin a demandé. L'inconnu, on le dit à l'adulte.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nina a demandé.
+narrateur|L'inconnu, on le dit à l'adulte.
+maman|Tu as demandé à maman ?
+enfant-f|Oui.
+maman|Bravo.
+maman|On demande à l'adulte.
+narrateur|La fraise était dans le panier.
+narrateur|L'herbe brille encore.
+narrateur|Le seau bleu est calme.
+maman|Tes mains étaient avec les feuilles ?
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1711,7 +1774,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman donne une fraise du panier. Marin dit merci.</t>
+          <t>Maman donne une fraise du panier. Nina dit merci. Tu as fini ta fraise ? Oui, maman. Bravo. Tu as fait du bon travail. Le panier est plus léger. Une goutte brille encore sur la feuille. Le marché fait encore un petit bruit. On rentre le panier ? Oui, maman. Elles prennent le panier ensemble.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1851,10 +1914,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman donne une fraise du panier. Marin dit merci.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Maman donne une fraise du panier.
+narrateur|Nina dit merci.
+maman|Tu as fini ta fraise ?
+enfant-f|Oui, maman.
+maman|Bravo. Tu as fait du bon travail.
+narrateur|Le panier est plus léger.
+narrateur|Une goutte brille encore sur la feuille.
+narrateur|Le marché fait encore un petit bruit.
+maman|On rentre le panier ?
+enfant-f|Oui, maman.
+narrateur|Elles prennent le panier ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1879,7 +1951,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a vu une baie inconnue. Elle a demandé à maman. Puis elle a goûté une fraise. Bravo, Nina. Merci, maman. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2019,10 +2091,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Nina a vu une baie inconnue.
+narrateur|Elle a demandé à maman.
+narrateur|Puis elle a goûté une fraise.
+maman|Bravo, Nina.
+enfant-f|Merci, maman.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2041,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2079,6 +2155,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.002-03.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-03.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>L'arrosoir penche dans l'herbe mouillée. Une goutte tombe sur une feuille. Une abeille passe tout près, tout doux. Le panier sent la terre tiède. Au loin, le marché fait un petit bruit. Nina, tu as vu l'herbe ? Oui, maman. Elle brille. Elle brille, après la pluie. Le jardin sent la terre mouillée. Un seau bleu est près du banc. Tu as vu le seau bleu ? Oui. Il est plein. Il est plein d'eau douce. En ce moment, Nina est au jardin. Ses chaussures sont un peu humides. Elle voit une baie brillante. La baie est ronde et rouge. Nina ne la connaît pas. C'est de l'inconnu. Nina pose les mains sur ses genoux. Elle va demander. Maman, je peux ? Tu demandes. C'est bien. Maman, c'est l'adulte. Maman regarde la baie. On laisse. Merci d'avoir demandé. On demande à l'adulte. Nina pose ses mains avec les feuilles. Les feuilles sont fraîches et lisses. On laisse, maman. Oui. Inconnu : on demande à l'adulte. Bravo, Nina. Maman ouvre le panier. Une fraise rouge attend. Celle-ci, tu la connais. Tu peux goûter. Nina prend la fraise. Elle est douce et un peu froide. Nina croque. C'est sucré. Merci, maman. Tu as fait du bon travail. Tu as demandé. L'arrosoir penche encore. L'abeille est déjà loin. Le seau bleu reste près du banc.</t>
+          <t>L'arrosoir penche dans l'herbe mouillée. Une goutte tombe sur une feuille. Une abeille passe tout près, tout doux. Le panier sent la terre tiède. Au loin, le marché fait un petit bruit. Nina, tu as vu l'herbe ? Oui, maman. Elle brille. Elle brille, après la pluie. Le jardin sent la terre mouillée. Un seau bleu est près du banc. Tu as vu le seau bleu ? Oui. Il est plein. Il est plein d'eau douce. En ce moment, Nina est au jardin. Ses chaussures sont un peu humides. Elle voit une baie brillante. La baie est ronde et rouge. Nina ne la connaît pas. C'est de l'inconnu. Nina pose les mains sur ses genoux. Elle va demander. Maman, je peux ? Tu demandes. C'est bien. Maman, c'est l'adulte. Maman regarde la baie. On laisse. Merci d'avoir demandé. On demande à l'adulte. Nina pose ses mains avec les feuilles. Les feuilles sont fraîches et lisses. On laisse, maman. Oui. Inconnu : on demande à l'adulte. Bravo, Nina. Maman ouvre le panier. Une fraise rouge attend. Celle-ci, tu la connais. Tu peux goûter. Nina prend la fraise. Elle est douce et un peu froide. Nina croque. C'est sucré. Merci, maman. Tu as demandé. L'arrosoir penche encore. L'abeille est déjà loin. Le seau bleu reste près du banc.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Marin est au jardin avec maman. Il voit une baie brillante. Il ne la connaît pas. C'est inconnu. Marin ne goûte pas tout seul. Il va &lt;emphasis level="moderate"&gt;demander&lt;/emphasis&gt;. Il dit : maman, je peux ? Maman, c'est l'adulte. Maman regarde. Elle dit : on laisse. Merci d'avoir demandé. Marin pose ses mains avec les feuilles. Inconnu : on demande à l'adulte.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'arrosoir penche dans l'herbe mouillée. Une goutte tombe sur une feuille. Une abeille passe tout près, tout doux. Le panier sent la terre tiède. Au loin, le marché fait un petit bruit. Nina, tu as vu l'herbe ? Oui, maman. Elle brille. Elle brille, après la pluie. Le jardin sent la terre mouillée. Un seau bleu est près du banc. Tu as vu le seau bleu ? Oui. Il est plein. Il est plein d'eau douce. En ce moment, Nina est au jardin. Ses chaussures sont un peu humides. Elle voit une baie brillante. La baie est ronde et rouge. Nina ne la connaît pas. C'est de l'inconnu. Nina pose les mains sur ses genoux. Elle va demander. Maman, je peux ? Tu demandes. C'est bien. Maman, c'est l'adulte. Maman regarde la baie. On laisse. Merci d'avoir demandé. On demande à l'adulte. Nina pose ses mains avec les feuilles. Les feuilles sont fraîches et lisses. On laisse, maman. Oui. Inconnu : on demande à l'adulte. Bravo, Nina. Maman ouvre le panier. Une fraise rouge attend. Celle-ci, tu la connais. Tu peux goûter. Nina prend la fraise. Elle est douce et un peu froide. Nina croque. C'est sucré. Merci, maman. Tu as demandé. L'arrosoir penche encore. L'abeille est déjà loin. Le seau bleu reste près du banc.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1366,7 +1366,6 @@
 narrateur|Nina croque.
 narrateur|C'est sucré.
 enfant-f|Merci, maman.
-maman|Tu as fait du bon travail.
 maman|Tu as demandé.
 narrateur|L'arrosoir penche encore.
 narrateur|L'abeille est déjà loin.
@@ -1402,7 +1401,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Marin voit une baie &lt;emphasis level="moderate"&gt;inconnu&lt;/emphasis&gt;e. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina voit une baie inconnue. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1594,7 +1593,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Marin a demandé. L'&lt;emphasis level="moderate"&gt;inconnu&lt;/emphasis&gt;, on le dit à l'adulte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a demandé. L'inconnu, on le dit à l'adulte. Tu as demandé à maman ? Oui. Bravo. On demande à l'adulte. La fraise était dans le panier. L'herbe brille encore. Le seau bleu est calme. Tes mains étaient avec les feuilles ? Oui, maman.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1774,12 +1773,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman donne une fraise du panier. Nina dit merci. Tu as fini ta fraise ? Oui, maman. Bravo. Tu as fait du bon travail. Le panier est plus léger. Une goutte brille encore sur la feuille. Le marché fait encore un petit bruit. On rentre le panier ? Oui, maman. Elles prennent le panier ensemble.</t>
+          <t>Maman donne une fraise du panier. Nina dit merci. Tu as fini ta fraise ? Oui, maman. Le panier est plus léger. Une goutte brille encore sur la feuille. Le marché fait encore un petit bruit. On rentre le panier ? Oui, maman. Elles prennent le panier ensemble.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Maman donne une fraise du panier. Marin dit merci.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman donne une fraise du panier. Nina dit merci. Tu as fini ta fraise ? Oui, maman. Le panier est plus léger. Une goutte brille encore sur la feuille. Le marché fait encore un petit bruit. On rentre le panier ? Oui, maman. Elles prennent le panier ensemble.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1918,7 +1917,6 @@
 narrateur|Nina dit merci.
 maman|Tu as fini ta fraise ?
 enfant-f|Oui, maman.
-maman|Bravo. Tu as fait du bon travail.
 narrateur|Le panier est plus léger.
 narrateur|Une goutte brille encore sur la feuille.
 narrateur|Le marché fait encore un petit bruit.
@@ -1951,12 +1949,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Nina a vu une baie inconnue. Elle a demandé à maman. Puis elle a goûté une fraise. Bravo, Nina. Merci, maman. L'histoire est finie.</t>
+          <t>Nina a vu une baie inconnue. Elle a demandé à maman. Puis elle a goûté une fraise. Bravo, Nina. Merci, maman.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a vu une baie inconnue. Elle a demandé à maman. Puis elle a goûté une fraise. Bravo, Nina. Merci, maman.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2095,8 +2093,7 @@
 narrateur|Elle a demandé à maman.
 narrateur|Puis elle a goûté une fraise.
 maman|Bravo, Nina.
-enfant-f|Merci, maman.
-narrateur|L'histoire est finie.</t>
+enfant-f|Merci, maman.</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2162,6 +2159,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.002-03.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-03.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Marin, maman</t>
+          <t>Nina, maman</t>
         </is>
       </c>
     </row>
